--- a/ExcelToJSONConverter/excel/guideQuest.xlsx
+++ b/ExcelToJSONConverter/excel/guideQuest.xlsx
@@ -3,14 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B6993C-C1A2-43E2-BB96-B16B3D4002BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90585ABF-8BED-41F6-9E3F-C42A7D4D99CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
-    <sheet name="s_guide_quest" sheetId="3" r:id="rId2"/>
-    <sheet name="s_guide_quest_repeat" sheetId="5" r:id="rId3"/>
+    <sheet name="s_quest_reward" sheetId="8" r:id="rId2"/>
+    <sheet name="s_quest" sheetId="6" r:id="rId3"/>
+    <sheet name="s_guide_quest" sheetId="3" r:id="rId4"/>
+    <sheet name="s_guide_quest_repeat" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="82">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -248,13 +250,67 @@
   </si>
   <si>
     <t>character_deploy</t>
+  </si>
+  <si>
+    <t>reward_item_key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login</t>
+  </si>
+  <si>
+    <t>gacha_proceed</t>
+  </si>
+  <si>
+    <t>rice_claim</t>
+  </si>
+  <si>
+    <t>gole_claim</t>
+  </si>
+  <si>
+    <t>office_dispatch</t>
+  </si>
+  <si>
+    <t>ads_watch</t>
+  </si>
+  <si>
+    <t>item_buy</t>
+  </si>
+  <si>
+    <t>item_use</t>
+  </si>
+  <si>
+    <t>daily</t>
+  </si>
+  <si>
+    <t>weekly</t>
+  </si>
+  <si>
+    <t>#reward_item_key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>daily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weekly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -285,6 +341,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -300,7 +362,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -323,13 +385,88 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -359,6 +496,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -698,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:E19"/>
+  <dimension ref="A2:E34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.5" bestFit="1" customWidth="1"/>
@@ -901,7 +1059,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -910,7 +1068,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -919,13 +1077,130 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>27</v>
       </c>
       <c r="B19">
         <f>B18+1</f>
         <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="10">
+        <v>0</v>
+      </c>
+      <c r="D22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="10">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="10">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -936,6 +1211,1114 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A3A4B6-E4EC-4DD7-BE85-83CEAF8B565E}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="6.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="11">
+        <f>VLOOKUP(A3,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="11">
+        <v>2</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="12">
+        <f>VLOOKUP(D3,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F3" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="11">
+        <f>VLOOKUP(A4,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="13">
+        <v>4</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="12">
+        <f>VLOOKUP(D4,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F4" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="11">
+        <f>VLOOKUP(A5,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="13">
+        <v>6</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="12">
+        <f>VLOOKUP(D5,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F5" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="11">
+        <f>VLOOKUP(A6,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="13">
+        <v>8</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="12">
+        <f>VLOOKUP(D6,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F6" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="11">
+        <f>VLOOKUP(A7,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="13">
+        <v>10</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="12">
+        <f>VLOOKUP(D7,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F7" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="11">
+        <f>VLOOKUP(A8,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="C8" s="13">
+        <v>2</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="12">
+        <f>VLOOKUP(D8,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F8" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="11">
+        <f>VLOOKUP(A9,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="13">
+        <v>4</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="12">
+        <f>VLOOKUP(D9,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F9" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="11">
+        <f>VLOOKUP(A10,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="13">
+        <v>6</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="12">
+        <f>VLOOKUP(D10,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F10" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="11">
+        <f>VLOOKUP(A11,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="C11" s="13">
+        <v>8</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="12">
+        <f>VLOOKUP(D11,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F11" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="11">
+        <f>VLOOKUP(A12,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="C12" s="13">
+        <v>10</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="12">
+        <f>VLOOKUP(D12,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F12" s="13">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BEDA713-557F-4C55-AA33-8B48011561E4}">
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="11">
+        <f>VLOOKUP(A3,Overview!A$22:B$34,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="11">
+        <f>VLOOKUP(C3,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="12">
+        <v>1</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="12">
+        <f>VLOOKUP(F3,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H3" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="11">
+        <f>VLOOKUP(A4,Overview!A$22:B$34,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="11">
+        <f>VLOOKUP(C4,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="14">
+        <v>5</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="12">
+        <f>VLOOKUP(F4,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H4" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="11">
+        <f>VLOOKUP(A5,Overview!A$22:B$34,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="11">
+        <f>VLOOKUP(C5,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="14">
+        <v>2</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="12">
+        <f>VLOOKUP(F5,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H5" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="11">
+        <f>VLOOKUP(A6,Overview!A$22:B$34,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="11">
+        <f>VLOOKUP(C6,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="14">
+        <v>1</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="12">
+        <f>VLOOKUP(F6,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H6" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="11">
+        <f>VLOOKUP(A7,Overview!A$22:B$34,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="11">
+        <f>VLOOKUP(C7,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="14">
+        <v>1</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="12">
+        <f>VLOOKUP(F7,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H7" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="11">
+        <f>VLOOKUP(A8,Overview!A$22:B$34,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="11">
+        <f>VLOOKUP(C8,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="12">
+        <f>VLOOKUP(F8,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H8" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="11">
+        <f>VLOOKUP(A9,Overview!A$22:B$34,2,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="11">
+        <f>VLOOKUP(C9,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="14">
+        <v>1</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="12">
+        <f>VLOOKUP(F9,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H9" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="11">
+        <f>VLOOKUP(A10,Overview!A$22:B$34,2,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="11">
+        <f>VLOOKUP(C10,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="14">
+        <v>3</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="12">
+        <f>VLOOKUP(F10,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H10" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="11">
+        <f>VLOOKUP(A11,Overview!A$22:B$34,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="11">
+        <f>VLOOKUP(C11,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="14">
+        <v>2</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="12">
+        <f>VLOOKUP(F11,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H11" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="11">
+        <f>VLOOKUP(A12,Overview!A$22:B$34,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="11">
+        <f>VLOOKUP(C12,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="14">
+        <v>1</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="12">
+        <f>VLOOKUP(F12,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H12" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="11">
+        <f>VLOOKUP(A13,Overview!A$22:B$34,2,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="11">
+        <f>VLOOKUP(C13,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="14">
+        <v>1</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="12">
+        <f>VLOOKUP(F13,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H13" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="11">
+        <f>VLOOKUP(A14,Overview!A$22:B$34,2,FALSE)</f>
+        <v>11</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="11">
+        <f>VLOOKUP(C14,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="14">
+        <v>1</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="12">
+        <f>VLOOKUP(F14,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H14" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="11">
+        <f>VLOOKUP(A15,Overview!A$22:B$34,2,FALSE)</f>
+        <v>12</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="11">
+        <f>VLOOKUP(C15,Overview!D$22:E$23,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="14">
+        <v>1</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="12">
+        <f>VLOOKUP(F15,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H15" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="11">
+        <f>VLOOKUP(A16,Overview!A$22:B$34,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="11">
+        <f>VLOOKUP(C16,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E16" s="14">
+        <v>7</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="12">
+        <f>VLOOKUP(F16,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H16" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="11">
+        <f>VLOOKUP(A17,Overview!A$22:B$34,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="11">
+        <f>VLOOKUP(C17,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E17" s="14">
+        <v>700</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="12">
+        <f>VLOOKUP(F17,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H17" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="11">
+        <f>VLOOKUP(A18,Overview!A$22:B$34,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="11">
+        <f>VLOOKUP(C18,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E18" s="14">
+        <v>14</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="12">
+        <f>VLOOKUP(F18,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H18" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="11">
+        <f>VLOOKUP(A19,Overview!A$22:B$34,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="11">
+        <f>VLOOKUP(C19,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E19" s="14">
+        <v>7</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="12">
+        <f>VLOOKUP(F19,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H19" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="11">
+        <f>VLOOKUP(A20,Overview!A$22:B$34,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="11">
+        <f>VLOOKUP(C20,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>7</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="12">
+        <f>VLOOKUP(F20,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H20" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="11">
+        <f>VLOOKUP(A21,Overview!A$22:B$34,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="11">
+        <f>VLOOKUP(C21,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E21" s="14">
+        <v>7</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="12">
+        <f>VLOOKUP(F21,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H21" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="11">
+        <f>VLOOKUP(A22,Overview!A$22:B$34,2,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="11">
+        <f>VLOOKUP(C22,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>7</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="12">
+        <f>VLOOKUP(F22,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H22" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="11">
+        <f>VLOOKUP(A23,Overview!A$22:B$34,2,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="11">
+        <f>VLOOKUP(C23,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="12">
+        <f>VLOOKUP(F23,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H23" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="11">
+        <f>VLOOKUP(A24,Overview!A$22:B$34,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="11">
+        <f>VLOOKUP(C24,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E24" s="14">
+        <v>14</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="12">
+        <f>VLOOKUP(F24,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H24" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="11">
+        <f>VLOOKUP(A25,Overview!A$22:B$34,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" s="11">
+        <f>VLOOKUP(C25,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E25" s="14">
+        <v>7</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="12">
+        <f>VLOOKUP(F25,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H25" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="11">
+        <f>VLOOKUP(A26,Overview!A$22:B$34,2,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="11">
+        <f>VLOOKUP(C26,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E26" s="14">
+        <v>7</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="12">
+        <f>VLOOKUP(F26,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H26" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="11">
+        <f>VLOOKUP(A27,Overview!A$22:B$34,2,FALSE)</f>
+        <v>11</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="11">
+        <f>VLOOKUP(C27,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>7</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="12">
+        <f>VLOOKUP(F27,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H27" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="11">
+        <f>VLOOKUP(A28,Overview!A$22:B$34,2,FALSE)</f>
+        <v>12</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" s="11">
+        <f>VLOOKUP(C28,Overview!D$22:E$23,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>7</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="12">
+        <f>VLOOKUP(F28,Overview!A$2:B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H28" s="14">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1164,7 +2547,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BF01C2-6BFB-4CCC-9124-BCB4513B4E3A}">
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>

--- a/ExcelToJSONConverter/excel/guideQuest.xlsx
+++ b/ExcelToJSONConverter/excel/guideQuest.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90585ABF-8BED-41F6-9E3F-C42A7D4D99CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D188D5A-325C-4DAD-8D47-43D33EE3A2CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -269,9 +269,6 @@
     <t>rice_claim</t>
   </si>
   <si>
-    <t>gole_claim</t>
-  </si>
-  <si>
     <t>office_dispatch</t>
   </si>
   <si>
@@ -303,6 +300,10 @@
   </si>
   <si>
     <t>#type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_claim</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1095,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1109,7 +1110,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1149,7 +1150,7 @@
     </row>
     <row r="28" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B28" s="10">
         <v>6</v>
@@ -1157,7 +1158,7 @@
     </row>
     <row r="29" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B29" s="10">
         <v>7</v>
@@ -1181,7 +1182,7 @@
     </row>
     <row r="32" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B32" s="10">
         <v>10</v>
@@ -1189,7 +1190,7 @@
     </row>
     <row r="33" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B33" s="10">
         <v>11</v>
@@ -1197,7 +1198,7 @@
     </row>
     <row r="34" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B34" s="10">
         <v>12</v>
@@ -1225,7 +1226,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>67</v>
@@ -1234,7 +1235,7 @@
         <v>5</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>66</v>
@@ -1265,7 +1266,7 @@
     </row>
     <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3" s="11">
         <f>VLOOKUP(A3,Overview!D$22:E$23,2,FALSE)</f>
@@ -1287,7 +1288,7 @@
     </row>
     <row r="4" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" s="11">
         <f>VLOOKUP(A4,Overview!D$22:E$23,2,FALSE)</f>
@@ -1304,12 +1305,13 @@
         <v>2</v>
       </c>
       <c r="F4" s="13">
-        <v>100</v>
+        <f>F3+100</f>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" s="11">
         <f>VLOOKUP(A5,Overview!D$22:E$23,2,FALSE)</f>
@@ -1326,12 +1328,13 @@
         <v>2</v>
       </c>
       <c r="F5" s="13">
-        <v>100</v>
+        <f t="shared" ref="F5:F12" si="0">F4+100</f>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" s="11">
         <f>VLOOKUP(A6,Overview!D$22:E$23,2,FALSE)</f>
@@ -1348,12 +1351,13 @@
         <v>2</v>
       </c>
       <c r="F6" s="13">
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" s="11">
         <f>VLOOKUP(A7,Overview!D$22:E$23,2,FALSE)</f>
@@ -1370,12 +1374,13 @@
         <v>2</v>
       </c>
       <c r="F7" s="13">
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8" s="11">
         <f>VLOOKUP(A8,Overview!D$22:E$23,2,FALSE)</f>
@@ -1392,12 +1397,13 @@
         <v>2</v>
       </c>
       <c r="F8" s="13">
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>600</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B9" s="11">
         <f>VLOOKUP(A9,Overview!D$22:E$23,2,FALSE)</f>
@@ -1414,12 +1420,13 @@
         <v>2</v>
       </c>
       <c r="F9" s="13">
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>700</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="11">
         <f>VLOOKUP(A10,Overview!D$22:E$23,2,FALSE)</f>
@@ -1436,12 +1443,13 @@
         <v>2</v>
       </c>
       <c r="F10" s="13">
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>800</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" s="11">
         <f>VLOOKUP(A11,Overview!D$22:E$23,2,FALSE)</f>
@@ -1458,12 +1466,13 @@
         <v>2</v>
       </c>
       <c r="F11" s="13">
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>900</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B12" s="11">
         <f>VLOOKUP(A12,Overview!D$22:E$23,2,FALSE)</f>
@@ -1480,7 +1489,8 @@
         <v>2</v>
       </c>
       <c r="F12" s="13">
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -1513,7 +1523,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>67</v>
@@ -1522,7 +1532,7 @@
         <v>5</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>66</v>
@@ -1566,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" s="11">
         <f>VLOOKUP(C3,Overview!D$22:E$23,2,FALSE)</f>
@@ -1595,14 +1605,15 @@
         <v>1</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" s="11">
         <f>VLOOKUP(C4,Overview!D$22:E$23,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E4" s="14">
-        <v>5</v>
+        <f>E3+1</f>
+        <v>2</v>
       </c>
       <c r="F4" s="14" t="s">
         <v>10</v>
@@ -1624,14 +1635,15 @@
         <v>2</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D5" s="11">
         <f>VLOOKUP(C5,Overview!D$22:E$23,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E5" s="14">
-        <v>2</v>
+        <f t="shared" ref="E5:E28" si="0">E4+1</f>
+        <v>3</v>
       </c>
       <c r="F5" s="14" t="s">
         <v>10</v>
@@ -1653,14 +1665,15 @@
         <v>3</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D6" s="11">
         <f>VLOOKUP(C6,Overview!D$22:E$23,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E6" s="14">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>10</v>
@@ -1682,14 +1695,15 @@
         <v>4</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7" s="11">
         <f>VLOOKUP(C7,Overview!D$22:E$23,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E7" s="14">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>10</v>
@@ -1711,14 +1725,15 @@
         <v>5</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D8" s="11">
         <f>VLOOKUP(C8,Overview!D$22:E$23,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E8" s="14">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>10</v>
@@ -1733,21 +1748,22 @@
     </row>
     <row r="9" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B9" s="11">
         <f>VLOOKUP(A9,Overview!A$22:B$34,2,FALSE)</f>
         <v>6</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D9" s="11">
         <f>VLOOKUP(C9,Overview!D$22:E$23,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E9" s="14">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="F9" s="14" t="s">
         <v>10</v>
@@ -1762,21 +1778,22 @@
     </row>
     <row r="10" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B10" s="11">
         <f>VLOOKUP(A10,Overview!A$22:B$34,2,FALSE)</f>
         <v>7</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D10" s="11">
         <f>VLOOKUP(C10,Overview!D$22:E$23,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E10" s="14">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="F10" s="14" t="s">
         <v>10</v>
@@ -1798,14 +1815,15 @@
         <v>8</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D11" s="11">
         <f>VLOOKUP(C11,Overview!D$22:E$23,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E11" s="14">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="F11" s="14" t="s">
         <v>10</v>
@@ -1827,14 +1845,15 @@
         <v>9</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D12" s="11">
         <f>VLOOKUP(C12,Overview!D$22:E$23,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E12" s="14">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="F12" s="14" t="s">
         <v>10</v>
@@ -1849,21 +1868,22 @@
     </row>
     <row r="13" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B13" s="11">
         <f>VLOOKUP(A13,Overview!A$22:B$34,2,FALSE)</f>
         <v>10</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" s="11">
         <f>VLOOKUP(C13,Overview!D$22:E$23,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E13" s="14">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="F13" s="14" t="s">
         <v>10</v>
@@ -1878,21 +1898,22 @@
     </row>
     <row r="14" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B14" s="11">
         <f>VLOOKUP(A14,Overview!A$22:B$34,2,FALSE)</f>
         <v>11</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" s="11">
         <f>VLOOKUP(C14,Overview!D$22:E$23,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="F14" s="14" t="s">
         <v>10</v>
@@ -1907,21 +1928,22 @@
     </row>
     <row r="15" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B15" s="11">
         <f>VLOOKUP(A15,Overview!A$22:B$34,2,FALSE)</f>
         <v>12</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" s="11">
         <f>VLOOKUP(C15,Overview!D$22:E$23,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E15" s="14">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="F15" s="14" t="s">
         <v>10</v>
@@ -1943,14 +1965,15 @@
         <v>0</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" s="11">
         <f>VLOOKUP(C16,Overview!D$22:E$23,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="F16" s="14" t="s">
         <v>10</v>
@@ -1972,14 +1995,15 @@
         <v>1</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D17" s="11">
         <f>VLOOKUP(C17,Overview!D$22:E$23,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>700</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="F17" s="14" t="s">
         <v>10</v>
@@ -2001,14 +2025,15 @@
         <v>2</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D18" s="11">
         <f>VLOOKUP(C18,Overview!D$22:E$23,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="F18" s="14" t="s">
         <v>10</v>
@@ -2030,14 +2055,15 @@
         <v>3</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D19" s="11">
         <f>VLOOKUP(C19,Overview!D$22:E$23,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="E19" s="14">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>17</v>
       </c>
       <c r="F19" s="14" t="s">
         <v>10</v>
@@ -2059,14 +2085,15 @@
         <v>4</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D20" s="11">
         <f>VLOOKUP(C20,Overview!D$22:E$23,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="F20" s="14" t="s">
         <v>10</v>
@@ -2088,14 +2115,15 @@
         <v>5</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D21" s="11">
         <f>VLOOKUP(C21,Overview!D$22:E$23,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="E21" s="14">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="F21" s="14" t="s">
         <v>10</v>
@@ -2110,21 +2138,22 @@
     </row>
     <row r="22" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B22" s="11">
         <f>VLOOKUP(A22,Overview!A$22:B$34,2,FALSE)</f>
         <v>6</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D22" s="11">
         <f>VLOOKUP(C22,Overview!D$22:E$23,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="E22" s="14">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="F22" s="14" t="s">
         <v>10</v>
@@ -2139,20 +2168,21 @@
     </row>
     <row r="23" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B23" s="11">
         <f>VLOOKUP(A23,Overview!A$22:B$34,2,FALSE)</f>
         <v>7</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D23" s="11">
         <f>VLOOKUP(C23,Overview!D$22:E$23,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="E23" s="14">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="F23" s="14" t="s">
@@ -2175,14 +2205,15 @@
         <v>8</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D24" s="11">
         <f>VLOOKUP(C24,Overview!D$22:E$23,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="E24" s="14">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
       <c r="F24" s="14" t="s">
         <v>10</v>
@@ -2204,14 +2235,15 @@
         <v>9</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D25" s="11">
         <f>VLOOKUP(C25,Overview!D$22:E$23,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="E25" s="14">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>23</v>
       </c>
       <c r="F25" s="14" t="s">
         <v>10</v>
@@ -2226,21 +2258,22 @@
     </row>
     <row r="26" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B26" s="11">
         <f>VLOOKUP(A26,Overview!A$22:B$34,2,FALSE)</f>
         <v>10</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D26" s="11">
         <f>VLOOKUP(C26,Overview!D$22:E$23,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="E26" s="14">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="F26" s="14" t="s">
         <v>10</v>
@@ -2255,21 +2288,22 @@
     </row>
     <row r="27" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B27" s="11">
         <f>VLOOKUP(A27,Overview!A$22:B$34,2,FALSE)</f>
         <v>11</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D27" s="11">
         <f>VLOOKUP(C27,Overview!D$22:E$23,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="E27" s="14">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="F27" s="14" t="s">
         <v>10</v>
@@ -2284,21 +2318,22 @@
     </row>
     <row r="28" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B28" s="11">
         <f>VLOOKUP(A28,Overview!A$22:B$34,2,FALSE)</f>
         <v>12</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D28" s="11">
         <f>VLOOKUP(C28,Overview!D$22:E$23,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>26</v>
       </c>
       <c r="F28" s="14" t="s">
         <v>10</v>

--- a/ExcelToJSONConverter/excel/guideQuest.xlsx
+++ b/ExcelToJSONConverter/excel/guideQuest.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3891F177-0646-4BED-8988-E720B44EA20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84D29B3-7F63-44E3-A3F5-4B10FD7AD878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>2</v>

--- a/ExcelToJSONConverter/excel/guideQuest.xlsx
+++ b/ExcelToJSONConverter/excel/guideQuest.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84D29B3-7F63-44E3-A3F5-4B10FD7AD878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D8DC20-767E-40EE-88B2-A1A13FAD994C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="92">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -244,10 +244,6 @@
   </si>
   <si>
     <t>weekly</t>
-  </si>
-  <si>
-    <t>#reward_item_key</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>daily</t>
@@ -925,7 +921,7 @@
     <row r="1" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -989,7 +985,7 @@
     </row>
     <row r="5" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
@@ -1011,7 +1007,7 @@
     </row>
     <row r="6" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
@@ -1033,7 +1029,7 @@
     </row>
     <row r="7" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
@@ -1055,7 +1051,7 @@
     </row>
     <row r="8" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
@@ -1069,7 +1065,7 @@
         <v>6</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H8" s="18">
         <v>6</v>
@@ -1077,7 +1073,7 @@
     </row>
     <row r="9" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
@@ -1099,7 +1095,7 @@
     </row>
     <row r="10" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
@@ -1121,7 +1117,7 @@
     </row>
     <row r="11" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
@@ -1136,7 +1132,7 @@
     </row>
     <row r="12" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
@@ -1151,7 +1147,7 @@
     </row>
     <row r="13" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
@@ -1166,7 +1162,7 @@
     </row>
     <row r="14" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
@@ -1181,7 +1177,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
@@ -1190,7 +1186,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
@@ -1199,7 +1195,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
@@ -1208,7 +1204,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
@@ -1235,7 +1231,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
@@ -1244,7 +1240,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1252,7 +1248,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1267,20 +1263,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A3A4B6-E4EC-4DD7-BE85-83CEAF8B565E}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="6.875" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="4" max="4" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>53</v>
@@ -1289,16 +1284,13 @@
         <v>5</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1314,11 +1306,8 @@
       <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
         <v>61</v>
       </c>
@@ -1332,15 +1321,11 @@
       <c r="D3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="11">
-        <f>VLOOKUP(D3,Overview!A$2:B$39,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F3" s="10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E3" s="10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>61</v>
       </c>
@@ -1354,16 +1339,12 @@
       <c r="D4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="11">
-        <f>VLOOKUP(D4,Overview!A$2:B$39,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F4" s="12">
-        <f>F3+100</f>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E4" s="12">
+        <f>E3+100</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>61</v>
       </c>
@@ -1377,16 +1358,12 @@
       <c r="D5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="11">
-        <f>VLOOKUP(D5,Overview!A$2:B$39,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F5" s="12">
-        <f t="shared" ref="F5:F12" si="0">F4+100</f>
+      <c r="E5" s="12">
+        <f t="shared" ref="E5:E12" si="0">E4+100</f>
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
         <v>61</v>
       </c>
@@ -1400,16 +1377,12 @@
       <c r="D6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="11">
-        <f>VLOOKUP(D6,Overview!A$2:B$39,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F6" s="12">
+      <c r="E6" s="12">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>61</v>
       </c>
@@ -1423,16 +1396,12 @@
       <c r="D7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="11">
-        <f>VLOOKUP(D7,Overview!A$2:B$39,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F7" s="12">
+      <c r="E7" s="12">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>62</v>
       </c>
@@ -1446,16 +1415,12 @@
       <c r="D8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="11">
-        <f>VLOOKUP(D8,Overview!A$2:B$39,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F8" s="12">
+      <c r="E8" s="12">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>62</v>
       </c>
@@ -1469,16 +1434,12 @@
       <c r="D9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="11">
-        <f>VLOOKUP(D9,Overview!A$2:B$39,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F9" s="12">
+      <c r="E9" s="12">
         <f t="shared" si="0"/>
         <v>700</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>62</v>
       </c>
@@ -1492,16 +1453,12 @@
       <c r="D10" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="11">
-        <f>VLOOKUP(D10,Overview!A$2:B$39,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F10" s="12">
+      <c r="E10" s="12">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>62</v>
       </c>
@@ -1515,16 +1472,12 @@
       <c r="D11" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="11">
-        <f>VLOOKUP(D11,Overview!A$2:B$39,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F11" s="12">
+      <c r="E11" s="12">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>62</v>
       </c>
@@ -1538,11 +1491,7 @@
       <c r="D12" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="11">
-        <f>VLOOKUP(D12,Overview!A$2:B$39,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F12" s="12">
+      <c r="E12" s="12">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
@@ -1569,22 +1518,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1612,7 +1561,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -1658,7 +1607,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -1704,7 +1653,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1750,7 +1699,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1796,7 +1745,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -1842,7 +1791,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -1888,7 +1837,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -1934,7 +1883,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -1980,7 +1929,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -2026,7 +1975,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -2072,7 +2021,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -2118,7 +2067,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -2164,7 +2113,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C27">
         <v>100</v>
@@ -2210,7 +2159,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -2256,7 +2205,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -2302,7 +2251,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -2348,7 +2297,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -2394,7 +2343,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -2440,7 +2389,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -2486,7 +2435,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C41">
         <v>100</v>
@@ -2532,7 +2481,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -2578,7 +2527,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C45">
         <v>100</v>
@@ -2624,7 +2573,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C47">
         <v>100</v>
@@ -2670,7 +2619,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C49">
         <v>100</v>
@@ -2716,7 +2665,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C51">
         <v>100</v>
@@ -2762,7 +2711,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C53">
         <v>100</v>
@@ -2808,7 +2757,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C55">
         <v>100</v>
@@ -2854,7 +2803,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C57">
         <v>100</v>
@@ -2900,7 +2849,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C59">
         <v>100</v>
@@ -2946,7 +2895,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C61">
         <v>100</v>
@@ -3019,19 +2968,19 @@
         <v>53</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -3200,7 +3149,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9" s="16">
         <f>VLOOKUP(A9,Overview!$G$2:$H$14, 2, FALSE)</f>
@@ -3503,7 +3452,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B22" s="16">
         <f>VLOOKUP(A22,Overview!$G$2:$H$14, 2, FALSE)</f>
@@ -3695,7 +3644,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>53</v>
@@ -3890,7 +3839,7 @@
     </row>
     <row r="9" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9" s="10">
         <f>VLOOKUP(A9,Overview!G$2:H$14,2,FALSE)</f>
@@ -4228,7 +4177,7 @@
     </row>
     <row r="22" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B22" s="10">
         <f>VLOOKUP(A22,Overview!G$2:H$14,2,FALSE)</f>

--- a/ExcelToJSONConverter/excel/guideQuest.xlsx
+++ b/ExcelToJSONConverter/excel/guideQuest.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D8DC20-767E-40EE-88B2-A1A13FAD994C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185E9062-F013-4765-804A-521986BCD3B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2944,7 +2944,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA592700-3ECC-4D17-B82E-628F6E33E3E6}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="9.375" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.125" bestFit="1" customWidth="1"/>
@@ -3224,44 +3224,38 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B12" s="16">
         <f>VLOOKUP(A12,Overview!$G$2:$H$14, 2, FALSE)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
       </c>
       <c r="D12" s="17">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="E12" s="17">
         <v>200</v>
       </c>
-      <c r="F12" s="17">
-        <v>1</v>
-      </c>
-      <c r="G12" s="17">
-        <v>1</v>
-      </c>
-      <c r="H12" s="17">
-        <v>1</v>
-      </c>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" s="16">
         <f>VLOOKUP(A13,Overview!$G$2:$H$14, 2, FALSE)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="17">
         <v>2</v>
       </c>
       <c r="D13" s="17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E13" s="17">
         <v>200</v>
@@ -3272,17 +3266,17 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="16">
         <f>VLOOKUP(A14,Overview!$G$2:$H$14, 2, FALSE)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" s="17">
         <v>2</v>
       </c>
       <c r="D14" s="17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E14" s="17">
         <v>200</v>
@@ -3293,20 +3287,20 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="16" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B15" s="16">
         <f>VLOOKUP(A15,Overview!$G$2:$H$14, 2, FALSE)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C15" s="17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" s="17">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E15" s="17">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F15" s="17"/>
       <c r="G15" s="17"/>
@@ -3314,38 +3308,44 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="16" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B16" s="16">
         <f>VLOOKUP(A16,Overview!$G$2:$H$14, 2, FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="17">
         <v>0</v>
       </c>
       <c r="D16" s="17">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="E16" s="17">
-        <v>50</v>
-      </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="F16" s="17">
+        <v>1</v>
+      </c>
+      <c r="G16" s="17">
+        <v>1</v>
+      </c>
+      <c r="H16" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="16">
         <f>VLOOKUP(A17,Overview!$G$2:$H$14, 2, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="17">
         <v>0</v>
       </c>
       <c r="D17" s="17">
-        <v>500</v>
+        <v>4</v>
       </c>
       <c r="E17" s="17">
         <v>100</v>
@@ -3362,44 +3362,38 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="16">
         <f>VLOOKUP(A18,Overview!$G$2:$H$14, 2, FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" s="17">
         <v>0</v>
       </c>
       <c r="D18" s="17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="17">
         <v>100</v>
       </c>
-      <c r="F18" s="17">
-        <v>1</v>
-      </c>
-      <c r="G18" s="17">
-        <v>1</v>
-      </c>
-      <c r="H18" s="17">
-        <v>1</v>
-      </c>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B19" s="16">
         <f>VLOOKUP(A19,Overview!$G$2:$H$14, 2, FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" s="17">
         <v>0</v>
       </c>
       <c r="D19" s="17">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E19" s="17">
         <v>100</v>
@@ -3410,17 +3404,17 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" s="16">
         <f>VLOOKUP(A20,Overview!$G$2:$H$14, 2, FALSE)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" s="17">
         <v>0</v>
       </c>
       <c r="D20" s="17">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="E20" s="17">
         <v>100</v>
@@ -3431,17 +3425,17 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B21" s="16">
         <f>VLOOKUP(A21,Overview!$G$2:$H$14, 2, FALSE)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" s="17">
         <v>0</v>
       </c>
       <c r="D21" s="17">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E21" s="17">
         <v>100</v>
@@ -3452,38 +3446,44 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B22" s="16">
         <f>VLOOKUP(A22,Overview!$G$2:$H$14, 2, FALSE)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22" s="17">
         <v>0</v>
       </c>
       <c r="D22" s="17">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="E22" s="17">
         <v>100</v>
       </c>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
+      <c r="F22" s="17">
+        <v>1</v>
+      </c>
+      <c r="G22" s="17">
+        <v>1</v>
+      </c>
+      <c r="H22" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B23" s="16">
         <f>VLOOKUP(A23,Overview!$G$2:$H$14, 2, FALSE)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" s="17">
         <v>0</v>
       </c>
       <c r="D23" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" s="17">
         <v>100</v>
@@ -3500,11 +3500,11 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B24" s="16">
         <f>VLOOKUP(A24,Overview!$G$2:$H$14, 2, FALSE)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C24" s="17">
         <v>0</v>
@@ -3515,56 +3515,44 @@
       <c r="E24" s="17">
         <v>100</v>
       </c>
-      <c r="F24" s="17">
-        <v>1</v>
-      </c>
-      <c r="G24" s="17">
-        <v>1</v>
-      </c>
-      <c r="H24" s="17">
-        <v>1</v>
-      </c>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B25" s="16">
         <f>VLOOKUP(A25,Overview!$G$2:$H$14, 2, FALSE)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C25" s="17">
         <v>0</v>
       </c>
       <c r="D25" s="17">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E25" s="17">
         <v>100</v>
       </c>
-      <c r="F25" s="17">
-        <v>1</v>
-      </c>
-      <c r="G25" s="17">
-        <v>1</v>
-      </c>
-      <c r="H25" s="17">
-        <v>1</v>
-      </c>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B26" s="16">
         <f>VLOOKUP(A26,Overview!$G$2:$H$14, 2, FALSE)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C26" s="17">
         <v>0</v>
       </c>
       <c r="D26" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" s="17">
         <v>100</v>
@@ -3572,48 +3560,6 @@
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
       <c r="H26" s="17"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="B27" s="16">
-        <f>VLOOKUP(A27,Overview!$G$2:$H$14, 2, FALSE)</f>
-        <v>11</v>
-      </c>
-      <c r="C27" s="17">
-        <v>0</v>
-      </c>
-      <c r="D27" s="17">
-        <v>2</v>
-      </c>
-      <c r="E27" s="17">
-        <v>100</v>
-      </c>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="16">
-        <f>VLOOKUP(A28,Overview!$G$2:$H$14, 2, FALSE)</f>
-        <v>12</v>
-      </c>
-      <c r="C28" s="17">
-        <v>0</v>
-      </c>
-      <c r="D28" s="17">
-        <v>5</v>
-      </c>
-      <c r="E28" s="17">
-        <v>100</v>
-      </c>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
